--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 12 September 2026 at 11:12 UTC</t>
+          <t>Generated 13 September 2026 at 12:15 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 13 September 2026 at 12:15 UTC</t>
+          <t>Generated 14 September 2026 at 13:17 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 14 September 2026 at 13:17 UTC</t>
+          <t>Generated 15 September 2026 at 12:03 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 15 September 2026 at 12:03 UTC</t>
+          <t>Generated 16 September 2026 at 11:59 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 16 September 2026 at 11:59 UTC</t>
+          <t>Generated 17 September 2026 at 12:01 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 17 September 2026 at 12:01 UTC</t>
+          <t>Generated 18 September 2026 at 11:43 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 18 September 2026 at 11:43 UTC</t>
+          <t>Generated 20 September 2026 at 09:01 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 20 September 2026 at 09:01 UTC</t>
+          <t>Generated 24 September 2026 at 12:56 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 24 September 2026 at 12:56 UTC</t>
+          <t>Generated 24 September 2026 at 14:15 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 24 September 2026 at 14:15 UTC</t>
+          <t>Generated 25 September 2026 at 23:08 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 25 September 2026 at 23:08 UTC</t>
+          <t>Generated 26 September 2026 at 11:45 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 25 September 2026 at 23:08 UTC</t>
+          <t>Generated 27 September 2026 at 19:44 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 27 September 2026 at 19:44 UTC</t>
+          <t>Generated 28 September 2026 at 14:33 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 28 September 2026 at 14:33 UTC</t>
+          <t>Generated 29 September 2026 at 00:18 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 29 September 2026 at 00:18 UTC</t>
+          <t>Generated 29 September 2026 at 13:21 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 29 September 2026 at 13:21 UTC</t>
+          <t>Generated 30 September 2026 at 13:02 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 30 September 2026 at 13:02 UTC</t>
+          <t>Generated 01 October 2026 at 13:53 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 01 October 2026 at 13:53 UTC</t>
+          <t>Generated 02 October 2026 at 13:09 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 02 October 2026 at 13:09 UTC</t>
+          <t>Generated 03 October 2026 at 12:01 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 03 October 2026 at 12:01 UTC</t>
+          <t>Generated 04 October 2026 at 05:29 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 04 October 2026 at 05:29 UTC</t>
+          <t>Generated 04 October 2026 at 12:51 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 04 October 2026 at 12:51 UTC</t>
+          <t>Generated 05 October 2026 at 15:16 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 05 October 2026 at 15:16 UTC</t>
+          <t>Generated 06 October 2026 at 13:39 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 06 October 2026 at 13:39 UTC</t>
+          <t>Generated 07 October 2026 at 13:52 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 07 October 2026 at 13:52 UTC</t>
+          <t>Generated 08 October 2026 at 14:00 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 08 October 2026 at 14:00 UTC</t>
+          <t>Generated 09 October 2026 at 13:44 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 09 October 2026 at 13:44 UTC</t>
+          <t>Generated 11 October 2026 at 15:38 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 11 October 2026 at 15:38 UTC</t>
+          <t>Generated 12 October 2026 at 11:56 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 12 October 2026 at 11:56 UTC</t>
+          <t>Generated 12 October 2026 at 16:03 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 12 October 2026 at 16:03 UTC</t>
+          <t>Generated 13 October 2026 at 14:36 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 13 October 2026 at 14:36 UTC</t>
+          <t>Generated 14 October 2026 at 12:22 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 14 October 2026 at 12:22 UTC</t>
+          <t>Generated 15 October 2026 at 12:05 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 15 October 2026 at 12:05 UTC</t>
+          <t>Generated 16 October 2026 at 11:55 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 16 October 2026 at 11:55 UTC</t>
+          <t>Generated 17 October 2026 at 11:11 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 17 October 2026 at 11:11 UTC</t>
+          <t>Generated 17 October 2026 at 19:07 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 17 October 2026 at 19:07 UTC</t>
+          <t>Generated 18 October 2026 at 05:31 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 18 October 2026 at 05:31 UTC</t>
+          <t>Generated 19 October 2026 at 13:56 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 19 October 2026 at 13:56 UTC</t>
+          <t>Generated 20 October 2026 at 12:04 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 20 October 2026 at 12:04 UTC</t>
+          <t>Generated 21 October 2026 at 12:21 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 21 October 2026 at 12:21 UTC</t>
+          <t>Generated 22 October 2026 at 12:24 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 22 October 2026 at 12:24 UTC</t>
+          <t>Generated 23 October 2026 at 12:07 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 23 October 2026 at 12:07 UTC</t>
+          <t>Generated 24 October 2026 at 11:35 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 24 October 2026 at 11:35 UTC</t>
+          <t>Generated 24 October 2026 at 19:23 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 24 October 2026 at 19:23 UTC</t>
+          <t>Generated 25 October 2026 at 06:32 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 25 October 2026 at 06:32 UTC</t>
+          <t>Generated 25 October 2026 at 12:03 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 25 October 2026 at 12:03 UTC</t>
+          <t>Generated 26 October 2026 at 13:37 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 26 October 2026 at 13:37 UTC</t>
+          <t>Generated 27 October 2026 at 12:45 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 27 October 2026 at 12:45 UTC</t>
+          <t>Generated 28 October 2026 at 13:35 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 28 October 2026 at 13:35 UTC</t>
+          <t>Generated 29 October 2026 at 13:44 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 29 October 2026 at 13:44 UTC</t>
+          <t>Generated 30 October 2026 at 13:33 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 30 October 2026 at 13:33 UTC</t>
+          <t>Generated 31 October 2026 at 13:07 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 31 October 2026 at 13:07 UTC</t>
+          <t>Generated 31 October 2026 at 20:31 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 31 October 2026 at 20:31 UTC</t>
+          <t>Generated 01 November 2026 at 06:34 UTC</t>
         </is>
       </c>
     </row>

--- a/samples/NVDA_company_profile.xlsx
+++ b/samples/NVDA_company_profile.xlsx
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Generated 01 November 2026 at 06:34 UTC</t>
+          <t>Generated 01 November 2026 at 13:51 UTC</t>
         </is>
       </c>
     </row>
